--- a/testdata/Product.xlsx
+++ b/testdata/Product.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0824946-BAB8-4A58-9391-541160E4007F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E248A6-744C-4AAF-AC70-EBCAF3C2EC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
   </bookViews>
   <sheets>
     <sheet name="addProduct" sheetId="5" r:id="rId1"/>
@@ -40,12 +40,6 @@
     <t xml:space="preserve"> expectedResult</t>
   </si>
   <si>
-    <t>Category 1</t>
-  </si>
-  <si>
-    <t>Category 2</t>
-  </si>
-  <si>
     <t>productName</t>
   </si>
   <si>
@@ -61,12 +55,6 @@
     <t xml:space="preserve"> productImage</t>
   </si>
   <si>
-    <t>Product 1</t>
-  </si>
-  <si>
-    <t>Product 2</t>
-  </si>
-  <si>
     <t>Lorem ipsum dolor sit amet, consectetur adipiscing elit. Integer nec odio. Praesent libero. Sed cursus ante dapibus diam. Sed nisi. Nulla quis sem at nibh elementum imperdiet. Duis sagittis ipsum. Praesent mauris.</t>
   </si>
   <si>
@@ -92,6 +80,18 @@
   </si>
   <si>
     <t>This product was successfully added</t>
+  </si>
+  <si>
+    <t>Cosmetic</t>
+  </si>
+  <si>
+    <t>Gadget</t>
+  </si>
+  <si>
+    <t>Smart Watch and Camera</t>
+  </si>
+  <si>
+    <t>Sun Screen</t>
   </si>
 </sst>
 </file>
@@ -487,19 +487,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -507,42 +507,42 @@
     </row>
     <row r="2" spans="1:6" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -564,19 +564,19 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
-      </c>
-      <c r="D1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
       <c r="F1" t="s">
         <v>0</v>
@@ -584,42 +584,42 @@
     </row>
     <row r="2" spans="1:6" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
         <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/testdata/Product.xlsx
+++ b/testdata/Product.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Sales Force\Automation\stp-automation-test\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08E248A6-744C-4AAF-AC70-EBCAF3C2EC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFA7F6B-6928-4CDD-9DAE-9703C1A13FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C7681F3F-D0BE-43DE-AC81-0EAE175E5E0E}"/>
   </bookViews>
